--- a/data_lake/reporte_cordoba_mes/dt=2026-07-20/CORDOBA_JUL26.xlsx
+++ b/data_lake/reporte_cordoba_mes/dt=2026-07-20/CORDOBA_JUL26.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="O:\Mi unidad\OSPA\02. Datos Diarios\Tablas\Datos hidrometeorologicos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E6E4165-3094-464F-B3CD-9E75F8548C44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2176ACE-25F1-49AF-8C91-DB9C92062134}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{5F8F14AC-D557-4126-B18A-7A2C1E69122F}"/>
   </bookViews>
@@ -10011,10 +10011,10 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>45.599999999999994</c:v>
+                  <c:v>73.599999999999994</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>-1</c:v>
+                  <c:v>109.30000000000001</c:v>
                 </c:pt>
                 <c:pt idx="19">
                   <c:v>-1</c:v>
@@ -19973,7 +19973,9 @@
       <c r="V3" s="25">
         <v>14.7</v>
       </c>
-      <c r="W3" s="25"/>
+      <c r="W3" s="25">
+        <v>0</v>
+      </c>
       <c r="X3" s="25"/>
       <c r="Y3" s="25"/>
       <c r="Z3" s="25"/>
@@ -20055,11 +20057,15 @@
       <c r="T4" s="25">
         <v>0</v>
       </c>
-      <c r="U4" s="25"/>
+      <c r="U4" s="25">
+        <v>0</v>
+      </c>
       <c r="V4" s="25">
         <v>20.2</v>
       </c>
-      <c r="W4" s="25"/>
+      <c r="W4" s="25">
+        <v>0</v>
+      </c>
       <c r="X4" s="25"/>
       <c r="Y4" s="25"/>
       <c r="Z4" s="25"/>
@@ -20147,7 +20153,9 @@
       <c r="V5" s="25">
         <v>1.3</v>
       </c>
-      <c r="W5" s="25"/>
+      <c r="W5" s="25">
+        <v>47</v>
+      </c>
       <c r="X5" s="25"/>
       <c r="Y5" s="25"/>
       <c r="Z5" s="25"/>
@@ -20162,7 +20170,7 @@
       <c r="AI5" s="34"/>
       <c r="AJ5" s="36">
         <f t="shared" si="0"/>
-        <v>109.39999999999999</v>
+        <v>156.39999999999998</v>
       </c>
       <c r="AK5" s="30">
         <v>40.986206896551728</v>
@@ -20235,7 +20243,9 @@
       <c r="V6" s="25">
         <v>1.4</v>
       </c>
-      <c r="W6" s="25"/>
+      <c r="W6" s="25">
+        <v>0.8</v>
+      </c>
       <c r="X6" s="25"/>
       <c r="Y6" s="25"/>
       <c r="Z6" s="25"/>
@@ -20250,7 +20260,7 @@
       <c r="AI6" s="34"/>
       <c r="AJ6" s="36">
         <f t="shared" si="0"/>
-        <v>109.7</v>
+        <v>110.5</v>
       </c>
       <c r="AK6" s="30">
         <v>88.719230769230762</v>
@@ -20427,7 +20437,9 @@
       <c r="V9" s="25">
         <v>8</v>
       </c>
-      <c r="W9" s="25"/>
+      <c r="W9" s="25">
+        <v>3</v>
+      </c>
       <c r="X9" s="25"/>
       <c r="Y9" s="25"/>
       <c r="Z9" s="25"/>
@@ -20442,7 +20454,7 @@
       <c r="AI9" s="34"/>
       <c r="AJ9" s="36">
         <f t="shared" si="0"/>
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="AK9" s="30">
         <v>65.482758620689651</v>
@@ -20591,7 +20603,9 @@
         <v>0</v>
       </c>
       <c r="V11" s="25"/>
-      <c r="W11" s="25"/>
+      <c r="W11" s="25">
+        <v>17.2</v>
+      </c>
       <c r="X11" s="25"/>
       <c r="Y11" s="25"/>
       <c r="Z11" s="25"/>
@@ -20606,7 +20620,7 @@
       <c r="AI11" s="34"/>
       <c r="AJ11" s="36">
         <f t="shared" si="0"/>
-        <v>130.4</v>
+        <v>147.6</v>
       </c>
       <c r="AK11" s="30">
         <v>19.188461538461539</v>
@@ -20677,7 +20691,9 @@
       <c r="V12" s="25">
         <v>0</v>
       </c>
-      <c r="W12" s="25"/>
+      <c r="W12" s="25">
+        <v>0.4</v>
+      </c>
       <c r="X12" s="25"/>
       <c r="Y12" s="25"/>
       <c r="Z12" s="25"/>
@@ -20692,7 +20708,7 @@
       <c r="AI12" s="34"/>
       <c r="AJ12" s="36">
         <f t="shared" si="0"/>
-        <v>50.3</v>
+        <v>50.699999999999996</v>
       </c>
       <c r="AK12" s="30">
         <v>34.724137931034484</v>
@@ -20762,8 +20778,12 @@
       <c r="U13" s="25">
         <v>0</v>
       </c>
-      <c r="V13" s="25"/>
-      <c r="W13" s="25"/>
+      <c r="V13" s="25">
+        <v>2</v>
+      </c>
+      <c r="W13" s="25">
+        <v>26</v>
+      </c>
       <c r="X13" s="25"/>
       <c r="Y13" s="25"/>
       <c r="Z13" s="25"/>
@@ -20778,7 +20798,7 @@
       <c r="AI13" s="34"/>
       <c r="AJ13" s="36">
         <f t="shared" si="0"/>
-        <v>42</v>
+        <v>70</v>
       </c>
       <c r="AK13" s="30"/>
     </row>
@@ -20849,7 +20869,9 @@
       <c r="V14" s="25">
         <v>0</v>
       </c>
-      <c r="W14" s="25"/>
+      <c r="W14" s="25">
+        <v>0</v>
+      </c>
       <c r="X14" s="25"/>
       <c r="Y14" s="25"/>
       <c r="Z14" s="25"/>
@@ -20934,8 +20956,12 @@
       <c r="U15" s="25">
         <v>0</v>
       </c>
-      <c r="V15" s="25"/>
-      <c r="W15" s="25"/>
+      <c r="V15" s="25">
+        <v>26</v>
+      </c>
+      <c r="W15" s="25">
+        <v>14.9</v>
+      </c>
       <c r="X15" s="25"/>
       <c r="Y15" s="25"/>
       <c r="Z15" s="25"/>
@@ -20950,7 +20976,7 @@
       <c r="AI15" s="34"/>
       <c r="AJ15" s="36">
         <f t="shared" si="0"/>
-        <v>89.4</v>
+        <v>130.30000000000001</v>
       </c>
       <c r="AK15" s="30">
         <v>60.46</v>
@@ -21128,11 +21154,11 @@
       </c>
       <c r="V19" s="26">
         <f t="shared" si="1"/>
-        <v>45.599999999999994</v>
+        <v>73.599999999999994</v>
       </c>
       <c r="W19" s="26">
         <f t="shared" si="1"/>
-        <v>-1</v>
+        <v>109.30000000000001</v>
       </c>
       <c r="X19" s="26">
         <f t="shared" si="1"/>
